--- a/course_registration_form_templates/005_masoretic_studies_registration--course_registration_form_templates.xlsx
+++ b/course_registration_form_templates/005_masoretic_studies_registration--course_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Contact Method Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consent Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Language Other</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_details_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contact Details</t>
+          <t>Contact Details 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
